--- a/docs/Table_S1_Interventions.xlsx
+++ b/docs/Table_S1_Interventions.xlsx
@@ -41,7 +41,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5EEF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF9F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFDF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDF4F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAF5FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -129,6 +154,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -496,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -546,34 +586,29 @@
           <t>Search date (n results)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Partial search strings</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Area-based conservation</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Fully protected area</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Non-temporary prohibition of all extractive activities and may or may not regulate access to the area to achieve biodiversity conservation objectives.</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Marine reserve, no-take area, no-go area, marine sancturay, etc</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>- Exclude all protected areas not Fully Protected (as per Grorud-Colvert et al. Science 2021) (no fishing, mining or dredging, and only minimal anchoring, infrastructure, aquaculture and non-extractive activities)
 - Exclude pelagic or deep water protected areas
@@ -581,65 +616,35 @@
 - Exclude Ridge-to-Reef protected areas (code as "Forest Conservation")</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>22/03/2023
 (n=5074)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>("locally-managed marine area*"
-  OR "community-based marine area*"
-  OR LMMA*
-  OR "fisher* closure*"
-  OR taboo* 
-  OR tabu* 
-  OR rahui 
-  OR "no-take"
-  OR "no take" 
-  OR "no-go zone*" 
-  OR "no go zone*" 
-  OR "fully protected area*" 
-  OR "partially protected area*" 
-  OR "integral reserve*"
-  OR OECM*
-  OR "other effective area-based conservation measures"
-  OR "other effective area based conservation measures" 
-  OR ((marine OR ocean) NEAR/3 ("protected area*" 
-                                OR reserve* 
-                                  OR closure* 
-                                  OR park* 
-                                  OR sanctuar* 
-                                  OR "conserv* area*" 
-                                OR "conserved territor*" 
-                                OR "restricted area*" 
-                                OR "community-based area*" )))</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Area-based conservation</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Partially protected area</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Regulation of “some extractive uses but permits others” to achieve biodiversity conservation objectives. </t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Marine park, multi-use MPA, buffer zones, etc.</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>- Exclude protected areas that are not Fully Protected (as per Grorud-Colvert et al. Science 2021) (no fishing, mining or dredging, and only minimal anchoring, infrastructure, aquaculture and non-extractive activities);
 - Exclude pelagic or deep water protected areas;
@@ -647,108 +652,97 @@
 - Exclude Ridge-to-Reef protected areas (code as "Forest Conservation")</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="F4" s="9" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Fisheries management</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Temporal closure</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Temporary prohibition of all extractive activities and may or may not regulate access to the area. Measures may include area and time restrictions, seasonal closures, time-of-day restrictions, periodically harvested closures, dynamic closure areas, some forms of rahui and taboos, etc.</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Area and time restrictions, periodically harvested closures, fishery restricted areas, dynamic closure area, seasonal closure, etc.</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>- Exclude taboos and other measures if they imply a complete and permanent ban of all/most activities (in line with the Fully Protected Areas definitiion above)
 - Exclude offshore (long-line) and shrimp (trawls) fisheries</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>23/04/2023
 (n=256)</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>(("periodic*" OR tempor* OR seasonal OR rotational OR dynamic OR "non-permanent") NEAR/3 (ban* OR closure* OR reserve* OR harvest*) OR "taboo" OR "taboos" OR "tabu" OR tabus OR rahui)</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Fisheries management</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Access right</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Restriction on fishing effort (input) to mitigate fishing pressure on the resource. Includes measures such as licenses, access rights, dive hours, number of lines or hooks, net setting time.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Customary marine tenure, spatial property rights, TURFs</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>- Exclude offshore (long-line) and shrimp (trawls) fisheries</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>23/05/2023
 (n=375)</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>(("fish*" NEAR/3 ("effort limit*" OR "restrict*" OR "effort control*" OR licens* OR "input control")) OR (("territorial use*" OR "area-based" OR fish* OR access) NEAR/3 right*))</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Fisheries management</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Gear-based management</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Restriction on, or modification of specific gear and fishing practices.</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Gear restriction areas, bycatch reduction technologies, etc.</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>- Exclude offshore (long-line) and shrimp (trawls) fisheries
 - Exclude fisheries' impact/sustainability assessments (except gear-management interventions are used as "impact" sites)
@@ -756,73 +750,63 @@
 - Exclude method development studies if only short-term (&lt;1 year) efficacy studied</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>02/07/2023
 (n=865)</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>(gear NEAR/3 (control OR restrict* OR closure* OR manag*)) OR ((bycatch OR "by-catch" OR "accidental catch*" OR discard) NEAR/3 (manag* OR reduc*))</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Fisheries management</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Catch restriction</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Restriction on catch (output) in order to reduce fishing pressure on the resource.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>catch-based rights, TAC, individual or transferrable quotas, catch shares, tradable rights</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>- Exclude offshore (long-line) and shrimp (trawls) fisheries</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>("catch restric*" OR "fishing quota*" OR "total allowable catch*", "catch share*")</t>
-        </is>
-      </c>
+      <c r="F8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Fisheries management</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Species restriction</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Restrictions on species and size implmented at the fishery or market-level.</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Size limits, species moratorium, species sales ban, etc.</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>- Include sales bans
 - Exclude seasonal species bans (code as "Temporal Closures")
@@ -830,68 +814,58 @@
 - Exclude offshore (long-line) and shrimp (trawls) fisheries</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>((species OR herbivore* OR parrotfish*) NEAR/3 (restriction* OR moratorium OR ban OR closure*)) OR ("mesh size" OR "size limit*" OR "size restrict*")</t>
-        </is>
-      </c>
+      <c r="F9" s="10" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Fisheries management</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Capacity reduction</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Payments for the permanent or temporary withdrawal of fishing boats, gear, fishing permits and licences, and gear to decrease fishing capacity.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>fishing vessel decommisioning, net buybacks, fishing licences, etc.</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>- Exclude offshore (long-line) and shrimp (trawls) fisheries</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>(buyback* OR "buy back*" OR "buy-back*" OR "buyout*" OR (fish* AND decommission*) OR (capacity NEAR/0 (manag* OR reduc*))</t>
-        </is>
-      </c>
+      <c r="F10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Watershed management</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Water systems improvement</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Planning and management of water quantity and quality, both input and output.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Drainage, sanitation systems, waste management, treatment plants, cesspool upgrades, health systems surveillance, etc.</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>- Include mangrove conservation and restoration programs;
 - Exclude studies not related to the marine ecosystem or tropical coastal communities;
@@ -900,94 +874,83 @@
 - Exclude method development studies</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>24/04/2023
 (n=2577)</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">((("agriculture" OR "livestock" OR "forest*" OR "logging" OR "on-farm" OR "catchment*") NEAR/10 ("sustainable" OR "conserv*" OR "restor*" OR "agro-ecol*" OR "eco-friendly" OR "runoff*" OR "run-off*" OR "erosion" ) NEAR ("manag*" OR "control*" OR "improve*" OR "best practice*" OR "best-practice*") OR "reforest*" OR "vegetated buffer*")
-  OR ((sewage* OR "waste water" OR cesspool* OR waste* OR drainage*) NEAR/10 ("manag*" OR "treat*" OR "improve*" OR "surveill*") OR "septic tank*")
-  OR ("ridge-to-reef" OR "ridge to reef" OR "land use planning" OR "land use management" OR "land-sea management")
-  OR ((("watershed*" OR "forest*") NEAR/10 ("restor*" OR "manag*" OR "conserv*" OR "protect*")) OR "reforest*" OR "vegetat* buffer*" OR "logging ban*" OR "terrestrial protected area*" ))
-</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Watershed management</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Land-use management</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Strategic regulation of the use of land.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Land-clearing ban, control of coastal development and coastline artificialization, improved agriculture practices, best-practice forestry, etc.</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Watershed management</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Forest conservation</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Preservation and protection of up-stream ecosystems.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Forests protection, reforestation, mangrove restoration, vegetated buffers, etc.</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr"/>
+      <c r="F13" s="11" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Bioengineering</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Transplantation &amp; restocking</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Release of all life-history stages after on-site collection and/or using aquaculture methods (=restocking ecological-relevant species)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>fish/coral/macroinvertebrates translocation, transplantation, larval propagation, restocking, etc.</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">- Exclude commercial aquaculture or translocation (should be coded as "Livelihoods diversification")
 - Exclude method development studies focusing on short-term efficacy (&lt; 12 months)
@@ -997,40 +960,35 @@
 </t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>28/06/2023
 (n=726)</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>((("coral" OR "mangrove") NEAR/3 ("restoration" OR "gardening" OR "outplant*" OR "rehab*" OR "farm*" OR "transloc*" OR "transplant*" OR "reloc*" OR "restock*"))  OR ("fish"  NEAR/3 ("stock enhancement" OR "restock*"))) AND (effect*     OR outcome* OR impact* OR assess* OR evaluat* OR benefit* OR efficienc* OR performance  OR compar*)</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Bioengineering</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Biocontrol</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Mechanical, chemical, or biological control of species that are considered to be invasive or pest.</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>COTS control, lionfish culling, macroalgae removal, rat eradication, etc.</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>- Include field experiments if applicable/similar to real-life intervention
 - Exlude field experiments that do not focus on species considered as invasive/pest
@@ -1038,139 +996,123 @@
 - Exclude method development studies focusing on short-term efficacy (&lt; 12months)</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>04/06/2023
 (n=443)</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>(("COTS" OR "crown-of-thorns" OR "crown of thorns" OR "acanthaster" OR "alga*" OR "macroalg*" OR "invasive" OR "pest" OR alien) NEAR/5 ("control" OR "bio-control" OR "biocontrol" OR "remov*" OR "cull*"))</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Bioengineering</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Coral treatment</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Support coral health and survival using probiotics, feeding, medicine or other treatments (+ shading ?)</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr"/>
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Exclude laboratories and aquariums applications</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>25/07/2023
 n=206</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>((coral*) NEAR/3 ("treatment*" OR "antibiotic*" OR "disease intervention*" OR "phage therapy" OR "antioxidant*" OR "nutritional supplement*") OR ("assisted evolution" OR "genetic enhancement" OR "generation* acclimatization" OR "selective breeding"))</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Bioengineering</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Assisted evolution</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Increase the thermal tolerance of natural coral populations via selective breeding or via synthetic biology and gene-engineering/editing approaches</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr"/>
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Exclude laboratories and aquariums applications</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Bioengineering</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Artificial structure</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Implementation of artificial reefs that are human made volontary deployed for purposes of coral reef restoration as a substrate for coral recruitment, coral planting, and/or for fish aggregation, recreationing.</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Artificial reefs, substrate stabilization</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>- Exclude studies of offshore marine ecosystems (e.g., effect of FADs), exclude ARs not volontary deployed (e.g. oil platform, shipwreck)
 - Exclude method development studies if only short-term (&lt; 12 months) efficacy studied
 - Exclude if corals have been attached to the structure (code as Coral Transplantation)</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>24/04/2023
 (n=664)</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>("artificial reef*" OR "artificial structure*" OR "eco-designed structure*" OR "rubble stabili*" OR "fish aggregating device*" OR "fish-aggregating device*" OR "fish attracting device" OR "FADs")</t>
-        </is>
-      </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Socioeconomic development</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Livelihood diversification</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Achieve a pattern of livelihood diversity to reduce poverty, vulnerability and pressure on natural resources.</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>alternative livelihoods, income diversification</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>- Exclude endogenous or unclear livelihood diversification processes (include exogenous diversification processes only)
 - Include all diversification pathways (balance, disparity, variety);
@@ -1178,53 +1120,43 @@
 - Exclude studies looking at other interventions' impact on livelihood</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>06/06/2023
 (n = 291)</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>((livelihood* OR income) NEAR/3 (diversi* OR alternat* OR portfolio*))</t>
-        </is>
-      </c>
     </row>
     <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Socioeconomic development</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>Social protection</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Set of long-term mechanisms designed combat chronic poverty as well as short-term measures to reduce the impact of shocks (Devereux and Sabates-Wheeler 2004;Barrientos and Hulme 2008) e.g., social safety-net programs, credits &amp; microloans</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Family planning, credit and loans, social safety-nets</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Exclude Livelihood diversification interventions (code as Livelihood diversification)</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>29/06/2023
 (n=197)</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>(((poverty NEAR/0 (allevia* OR reduct* OR relief)) OR (social NEAR/0 (work OR assistance OR insurance* OR care OR transfer*)) OR ("welfare polic*" OR "welfare program*" OR "direct payment*" OR "family planning")))</t>
         </is>
       </c>
     </row>
